--- a/visuals/ownership-rate-by-re-hhsize.xlsx
+++ b/visuals/ownership-rate-by-re-hhsize.xlsx
@@ -28692,7 +28692,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -36217,63 +36217,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>People of color</t>
+          <t>Native Hawaiian or Pacific Islander</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>detail</t>
-        </is>
-      </c>
-      <c r="E98">
-        <v>7451</v>
-      </c>
-      <c r="F98">
-        <v>7438</v>
-      </c>
-      <c r="G98">
-        <v>7451</v>
-      </c>
-      <c r="H98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="I98">
-        <v>0.467123029579853</v>
-      </c>
-      <c r="J98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="K98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="L98">
-        <v>900.154160944113</v>
-      </c>
-      <c r="M98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="N98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="O98">
-        <v>0.0364220347435384</v>
-      </c>
-      <c r="P98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>good</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -36296,7 +36245,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Single race Harvard</t>
+          <t>People of color</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -36305,40 +36254,40 @@
         </is>
       </c>
       <c r="E99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="F99">
-        <v>39374</v>
+        <v>7438</v>
       </c>
       <c r="G99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="H99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="I99">
-        <v>0.546489194853502</v>
+        <v>0.467123029579853</v>
       </c>
       <c r="J99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="K99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="L99">
-        <v>1805.82339111519</v>
+        <v>900.154160944113</v>
       </c>
       <c r="M99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="N99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="O99">
-        <v>0.0194057161155801</v>
+        <v>0.0364220347435384</v>
       </c>
       <c r="P99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -36375,7 +36324,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Single race PSRC</t>
+          <t>Single race Harvard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -36384,40 +36333,40 @@
         </is>
       </c>
       <c r="E100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="F100">
-        <v>37820</v>
+        <v>39374</v>
       </c>
       <c r="G100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="H100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I100">
-        <v>0.550990675990676</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L100">
-        <v>1812.88374167788</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O100">
-        <v>0.0204756514200509</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -36533,7 +36482,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Some Other Race</t>
+          <t>Single race PSRC</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -36542,54 +36491,54 @@
         </is>
       </c>
       <c r="E102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="F102">
-        <v>219</v>
+        <v>37820</v>
       </c>
       <c r="G102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="H102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="I102">
-        <v>0.384885764499121</v>
+        <v>0.550990675990676</v>
       </c>
       <c r="J102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="K102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="L102">
-        <v>130.865410704089</v>
+        <v>1812.88374167788</v>
       </c>
       <c r="M102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="N102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="O102">
-        <v>0.183116547771441</v>
+        <v>0.0204756514200509</v>
       </c>
       <c r="P102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -36612,7 +36561,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Some Other Race</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -36621,54 +36570,54 @@
         </is>
       </c>
       <c r="E103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="F103">
-        <v>39374</v>
+        <v>219</v>
       </c>
       <c r="G103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="H103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="I103">
-        <v>0.546489194853502</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="J103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="K103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="L103">
-        <v>1805.82339111519</v>
+        <v>130.865410704089</v>
       </c>
       <c r="M103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="N103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="O103">
-        <v>0.0194057161155801</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="P103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -36928,7 +36877,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Two or More Races</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -36937,54 +36886,54 @@
         </is>
       </c>
       <c r="E107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="F107">
-        <v>1554</v>
+        <v>39374</v>
       </c>
       <c r="G107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="H107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I107">
-        <v>0.455852156057495</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L107">
-        <v>398.852461461315</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O107">
-        <v>0.0726113735226537</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -37086,7 +37035,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Two or More Races</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -37095,54 +37044,54 @@
         </is>
       </c>
       <c r="E109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="F109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="G109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="H109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="I109">
-        <v>0.569005452018672</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="J109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="K109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="L109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="M109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="N109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="O109">
-        <v>0.0211536420417412</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="P109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -37231,6 +37180,85 @@
       </c>
       <c r="U110">
         <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2023</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Snohomish</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E111">
+        <v>31936</v>
+      </c>
+      <c r="F111">
+        <v>31936</v>
+      </c>
+      <c r="G111">
+        <v>31936</v>
+      </c>
+      <c r="H111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="I111">
+        <v>0.569005452018672</v>
+      </c>
+      <c r="J111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="K111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="L111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="M111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="N111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="O111">
+        <v>0.0211536420417412</v>
+      </c>
+      <c r="P111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>single-person</t>
+        </is>
+      </c>
+      <c r="U111">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -37240,7 +37268,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -44765,63 +44793,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>People of color</t>
+          <t>Native Hawaiian or Pacific Islander</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>dichot</t>
-        </is>
-      </c>
-      <c r="E98">
-        <v>7451</v>
-      </c>
-      <c r="F98">
-        <v>7438</v>
-      </c>
-      <c r="G98">
-        <v>7451</v>
-      </c>
-      <c r="H98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="I98">
-        <v>0.467123029579853</v>
-      </c>
-      <c r="J98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="K98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="L98">
-        <v>900.154160944113</v>
-      </c>
-      <c r="M98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="N98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="O98">
-        <v>0.0364220347435384</v>
-      </c>
-      <c r="P98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>good</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -44844,7 +44821,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Single race Harvard</t>
+          <t>People of color</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -44853,40 +44830,40 @@
         </is>
       </c>
       <c r="E99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="F99">
-        <v>39374</v>
+        <v>7438</v>
       </c>
       <c r="G99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="H99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="I99">
-        <v>0.546489194853502</v>
+        <v>0.467123029579853</v>
       </c>
       <c r="J99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="K99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="L99">
-        <v>1805.82339111519</v>
+        <v>900.154160944113</v>
       </c>
       <c r="M99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="N99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="O99">
-        <v>0.0194057161155801</v>
+        <v>0.0364220347435384</v>
       </c>
       <c r="P99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -44923,7 +44900,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Single race PSRC</t>
+          <t>Single race Harvard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -44932,40 +44909,40 @@
         </is>
       </c>
       <c r="E100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="F100">
-        <v>37820</v>
+        <v>39374</v>
       </c>
       <c r="G100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="H100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I100">
-        <v>0.550990675990676</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L100">
-        <v>1812.88374167788</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O100">
-        <v>0.0204756514200509</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -45081,7 +45058,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Some Other Race</t>
+          <t>Single race PSRC</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -45090,54 +45067,54 @@
         </is>
       </c>
       <c r="E102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="F102">
-        <v>219</v>
+        <v>37820</v>
       </c>
       <c r="G102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="H102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="I102">
-        <v>0.384885764499121</v>
+        <v>0.550990675990676</v>
       </c>
       <c r="J102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="K102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="L102">
-        <v>130.865410704089</v>
+        <v>1812.88374167788</v>
       </c>
       <c r="M102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="N102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="O102">
-        <v>0.183116547771441</v>
+        <v>0.0204756514200509</v>
       </c>
       <c r="P102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -45160,7 +45137,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Some Other Race</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -45169,54 +45146,54 @@
         </is>
       </c>
       <c r="E103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="F103">
-        <v>39374</v>
+        <v>219</v>
       </c>
       <c r="G103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="H103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="I103">
-        <v>0.546489194853502</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="J103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="K103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="L103">
-        <v>1805.82339111519</v>
+        <v>130.865410704089</v>
       </c>
       <c r="M103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="N103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="O103">
-        <v>0.0194057161155801</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="P103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -45476,7 +45453,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Two or More Races</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -45485,54 +45462,54 @@
         </is>
       </c>
       <c r="E107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="F107">
-        <v>1554</v>
+        <v>39374</v>
       </c>
       <c r="G107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="H107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I107">
-        <v>0.455852156057495</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L107">
-        <v>398.852461461315</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O107">
-        <v>0.0726113735226537</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -45634,7 +45611,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Two or More Races</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -45643,54 +45620,54 @@
         </is>
       </c>
       <c r="E109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="F109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="G109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="H109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="I109">
-        <v>0.569005452018672</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="J109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="K109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="L109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="M109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="N109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="O109">
-        <v>0.0211536420417412</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="P109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -45779,6 +45756,85 @@
       </c>
       <c r="U110">
         <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2023</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Snohomish</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>dichot</t>
+        </is>
+      </c>
+      <c r="E111">
+        <v>31936</v>
+      </c>
+      <c r="F111">
+        <v>31936</v>
+      </c>
+      <c r="G111">
+        <v>31936</v>
+      </c>
+      <c r="H111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="I111">
+        <v>0.569005452018672</v>
+      </c>
+      <c r="J111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="K111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="L111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="M111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="N111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="O111">
+        <v>0.0211536420417412</v>
+      </c>
+      <c r="P111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>single-person</t>
+        </is>
+      </c>
+      <c r="U111">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -45788,7 +45844,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U110"/>
+  <dimension ref="A1:U111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -53313,63 +53369,12 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>People of color</t>
+          <t>Native Hawaiian or Pacific Islander</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>single</t>
-        </is>
-      </c>
-      <c r="E98">
-        <v>7451</v>
-      </c>
-      <c r="F98">
-        <v>7438</v>
-      </c>
-      <c r="G98">
-        <v>7451</v>
-      </c>
-      <c r="H98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="I98">
-        <v>0.467123029579853</v>
-      </c>
-      <c r="J98">
-        <v>0.464757984031936</v>
-      </c>
-      <c r="K98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="L98">
-        <v>900.154160944113</v>
-      </c>
-      <c r="M98">
-        <v>903.529783524041</v>
-      </c>
-      <c r="N98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="O98">
-        <v>0.0364220347435384</v>
-      </c>
-      <c r="P98">
-        <v>0.0373840028183127</v>
-      </c>
-      <c r="Q98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>good</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -53392,7 +53397,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Single race Harvard</t>
+          <t>People of color</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -53401,40 +53406,40 @@
         </is>
       </c>
       <c r="E99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="F99">
-        <v>39374</v>
+        <v>7438</v>
       </c>
       <c r="G99">
-        <v>39387</v>
+        <v>7451</v>
       </c>
       <c r="H99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="I99">
-        <v>0.546489194853502</v>
+        <v>0.467123029579853</v>
       </c>
       <c r="J99">
-        <v>0.545662353495331</v>
+        <v>0.464757984031936</v>
       </c>
       <c r="K99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="L99">
-        <v>1805.82339111519</v>
+        <v>900.154160944113</v>
       </c>
       <c r="M99">
-        <v>1809.53540454</v>
+        <v>903.529783524041</v>
       </c>
       <c r="N99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="O99">
-        <v>0.0194057161155801</v>
+        <v>0.0364220347435384</v>
       </c>
       <c r="P99">
-        <v>0.0196297044202006</v>
+        <v>0.0373840028183127</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
@@ -53471,7 +53476,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Single race PSRC</t>
+          <t>Single race Harvard</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -53480,40 +53485,40 @@
         </is>
       </c>
       <c r="E100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="F100">
-        <v>37820</v>
+        <v>39374</v>
       </c>
       <c r="G100">
-        <v>37833</v>
+        <v>39387</v>
       </c>
       <c r="H100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I100">
-        <v>0.550990675990676</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J100">
-        <v>0.550114143631949</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L100">
-        <v>1812.88374167788</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M100">
-        <v>1816.67211837263</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O100">
-        <v>0.0204756514200509</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P100">
-        <v>0.0206838997758817</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
@@ -53629,7 +53634,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Some Other Race</t>
+          <t>Single race PSRC</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -53638,54 +53643,54 @@
         </is>
       </c>
       <c r="E102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="F102">
-        <v>219</v>
+        <v>37820</v>
       </c>
       <c r="G102">
-        <v>219</v>
+        <v>37833</v>
       </c>
       <c r="H102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="I102">
-        <v>0.384885764499121</v>
+        <v>0.550990675990676</v>
       </c>
       <c r="J102">
-        <v>0.384885764499121</v>
+        <v>0.550114143631949</v>
       </c>
       <c r="K102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="L102">
-        <v>130.865410704089</v>
+        <v>1812.88374167788</v>
       </c>
       <c r="M102">
-        <v>130.865410704089</v>
+        <v>1816.67211837263</v>
       </c>
       <c r="N102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="O102">
-        <v>0.183116547771441</v>
+        <v>0.0204756514200509</v>
       </c>
       <c r="P102">
-        <v>0.183116547771441</v>
+        <v>0.0206838997758817</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>weak</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T102" t="inlineStr">
@@ -53708,7 +53713,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Region</t>
+          <t>Some Other Race</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -53717,54 +53722,54 @@
         </is>
       </c>
       <c r="E103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="F103">
-        <v>39374</v>
+        <v>219</v>
       </c>
       <c r="G103">
-        <v>39387</v>
+        <v>219</v>
       </c>
       <c r="H103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="I103">
-        <v>0.546489194853502</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="J103">
-        <v>0.545662353495331</v>
+        <v>0.384885764499121</v>
       </c>
       <c r="K103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="L103">
-        <v>1805.82339111519</v>
+        <v>130.865410704089</v>
       </c>
       <c r="M103">
-        <v>1809.53540454</v>
+        <v>130.865410704089</v>
       </c>
       <c r="N103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="O103">
-        <v>0.0194057161155801</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="P103">
-        <v>0.0196297044202006</v>
+        <v>0.183116547771441</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>weak</t>
         </is>
       </c>
       <c r="T103" t="inlineStr">
@@ -54024,7 +54029,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Two or More Races</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -54033,54 +54038,54 @@
         </is>
       </c>
       <c r="E107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="F107">
-        <v>1554</v>
+        <v>39374</v>
       </c>
       <c r="G107">
-        <v>1554</v>
+        <v>39387</v>
       </c>
       <c r="H107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="I107">
-        <v>0.455852156057495</v>
+        <v>0.546489194853502</v>
       </c>
       <c r="J107">
-        <v>0.455852156057495</v>
+        <v>0.545662353495331</v>
       </c>
       <c r="K107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="L107">
-        <v>398.852461461315</v>
+        <v>1805.82339111519</v>
       </c>
       <c r="M107">
-        <v>398.852461461315</v>
+        <v>1809.53540454</v>
       </c>
       <c r="N107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="O107">
-        <v>0.0726113735226537</v>
+        <v>0.0194057161155801</v>
       </c>
       <c r="P107">
-        <v>0.0726113735226537</v>
+        <v>0.0196297044202006</v>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>fair</t>
+          <t>good</t>
         </is>
       </c>
       <c r="T107" t="inlineStr">
@@ -54182,7 +54187,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>White</t>
+          <t>Two or More Races</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -54191,54 +54196,54 @@
         </is>
       </c>
       <c r="E109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="F109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="G109">
-        <v>31936</v>
+        <v>1554</v>
       </c>
       <c r="H109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="I109">
-        <v>0.569005452018672</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="J109">
-        <v>0.568762243989314</v>
+        <v>0.455852156057495</v>
       </c>
       <c r="K109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="L109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="M109">
-        <v>1583.12354872535</v>
+        <v>398.852461461315</v>
       </c>
       <c r="N109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="O109">
-        <v>0.0211536420417412</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="P109">
-        <v>0.0211868506395508</v>
+        <v>0.0726113735226537</v>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="T109" t="inlineStr">
@@ -54327,6 +54332,85 @@
       </c>
       <c r="U110">
         <v>21</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>2023</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Snohomish</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="E111">
+        <v>31936</v>
+      </c>
+      <c r="F111">
+        <v>31936</v>
+      </c>
+      <c r="G111">
+        <v>31936</v>
+      </c>
+      <c r="H111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="I111">
+        <v>0.569005452018672</v>
+      </c>
+      <c r="J111">
+        <v>0.568762243989314</v>
+      </c>
+      <c r="K111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="L111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="M111">
+        <v>1583.12354872535</v>
+      </c>
+      <c r="N111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="O111">
+        <v>0.0211536420417412</v>
+      </c>
+      <c r="P111">
+        <v>0.0211868506395508</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>single-person</t>
+        </is>
+      </c>
+      <c r="U111">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
